--- a/excel-files/QUEZON CITY/NOH-SCHOOL FOR CRIPPLED CHILDREN.xlsx
+++ b/excel-files/QUEZON CITY/NOH-SCHOOL FOR CRIPPLED CHILDREN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10403"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="226" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{609FFBDE-CB15-44B5-8C28-EA4CEE498A78}"/>
+  <xr:revisionPtr revIDLastSave="280" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1518358-1482-2A41-9AD2-F222FC9EB700}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -309,12 +309,18 @@
   <si>
     <t>Arts</t>
   </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>RO</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1826,13 +1832,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1853,6 +1852,53 @@
         <patternFill patternType="solid">
           <fgColor rgb="FF000000"/>
           <bgColor rgb="FFCAEDFB"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Bookman Old Style"/>
+        <family val="1"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2934,13 +2980,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2972,39 +3011,6 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Bookman Old Style"/>
-        <family val="1"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -3019,7 +3025,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="32" headerRowBorderDxfId="31" tableBorderDxfId="30">
   <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
@@ -3036,54 +3042,54 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="61" headerRowBorderDxfId="62" tableBorderDxfId="60">
   <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{945324E6-140A-476C-A8C3-23A16D4D262F}" name="Enrolment S.Y. 2025-2026 " dataDxfId="54"/>
-    <tableColumn id="4" xr3:uid="{A2D4C0AF-3699-4D3C-A791-2D7D8004CC89}" name="Quantity based on Target LAS - Q1 " dataDxfId="53">
+    <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{945324E6-140A-476C-A8C3-23A16D4D262F}" name="Enrolment S.Y. 2025-2026 " dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{A2D4C0AF-3699-4D3C-A791-2D7D8004CC89}" name="Quantity based on Target LAS - Q1 " dataDxfId="56">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9CE2D7B1-8761-49A3-A313-E7834B16687D}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q1" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{FCD520AB-D938-4542-9B56-AEC07AB5F1DC}" name="Year of Delivery-LAS - Q1" dataDxfId="51"/>
-    <tableColumn id="7" xr3:uid="{674474DE-9D20-41C1-8261-DA9C4A95671C}" name="SOURCE - LAS (CO,RO, SDO) - Q1" dataDxfId="50"/>
-    <tableColumn id="8" xr3:uid="{58D9CB98-8F6F-4F61-9103-C27B8FFBDB51}" name="GAP - LAS - Q1" dataDxfId="49">
+    <tableColumn id="5" xr3:uid="{9CE2D7B1-8761-49A3-A313-E7834B16687D}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q1" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{FCD520AB-D938-4542-9B56-AEC07AB5F1DC}" name="Year of Delivery-LAS - Q1" dataDxfId="54"/>
+    <tableColumn id="7" xr3:uid="{674474DE-9D20-41C1-8261-DA9C4A95671C}" name="SOURCE - LAS (CO,RO, SDO) - Q1" dataDxfId="53"/>
+    <tableColumn id="8" xr3:uid="{58D9CB98-8F6F-4F61-9103-C27B8FFBDB51}" name="GAP - LAS - Q1" dataDxfId="52">
       <calculatedColumnFormula>IF((D3-E3)&lt;0,0,(D3-E3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E6406FC4-4491-4FD6-9EA2-F088E94C44F4}" name="SURPLUS - LAS - Q1" dataDxfId="48">
+    <tableColumn id="9" xr3:uid="{E6406FC4-4491-4FD6-9EA2-F088E94C44F4}" name="SURPLUS - LAS - Q1" dataDxfId="51">
       <calculatedColumnFormula>IF((E3-D3)&lt;0,0,(E3-D3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1E56D889-DC27-4BCB-B61E-06BBBE734949}" name="Quantity based on Target LAS - Q2" dataDxfId="47">
+    <tableColumn id="10" xr3:uid="{1E56D889-DC27-4BCB-B61E-06BBBE734949}" name="Quantity based on Target LAS - Q2" dataDxfId="50">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{E933BF99-834C-4F15-8181-7D005013BD85}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) Q2" dataDxfId="46"/>
-    <tableColumn id="12" xr3:uid="{F2E2CB95-E0BD-4C6E-ACFE-F201177004A0}" name="Year of Delivery-LAS Q2" dataDxfId="45"/>
-    <tableColumn id="13" xr3:uid="{163FBFFB-0AB7-44C8-89C4-72AA64C1EAC7}" name="SOURCE-LAS (CO,RO, SDO) Q2" dataDxfId="44"/>
-    <tableColumn id="14" xr3:uid="{EACC05A8-C68D-4495-BC08-73F093C4992F}" name="GAP - LAS -Q2" dataDxfId="43"/>
-    <tableColumn id="15" xr3:uid="{28A44E24-3E28-4B7F-BADE-28BB84F0B810}" name="SURPLUS - LAS -Q2" dataDxfId="42"/>
-    <tableColumn id="16" xr3:uid="{87878677-5715-46B6-9BA9-9D08DE9A3335}" name="Quantity based on Target LAS - Q3" dataDxfId="41">
+    <tableColumn id="11" xr3:uid="{E933BF99-834C-4F15-8181-7D005013BD85}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) Q2" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{F2E2CB95-E0BD-4C6E-ACFE-F201177004A0}" name="Year of Delivery-LAS Q2" dataDxfId="48"/>
+    <tableColumn id="13" xr3:uid="{163FBFFB-0AB7-44C8-89C4-72AA64C1EAC7}" name="SOURCE-LAS (CO,RO, SDO) Q2" dataDxfId="47"/>
+    <tableColumn id="14" xr3:uid="{EACC05A8-C68D-4495-BC08-73F093C4992F}" name="GAP - LAS -Q2" dataDxfId="46"/>
+    <tableColumn id="15" xr3:uid="{28A44E24-3E28-4B7F-BADE-28BB84F0B810}" name="SURPLUS - LAS -Q2" dataDxfId="45"/>
+    <tableColumn id="16" xr3:uid="{87878677-5715-46B6-9BA9-9D08DE9A3335}" name="Quantity based on Target LAS - Q3" dataDxfId="44">
       <calculatedColumnFormula>#REF!*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{48667A1F-77B1-47A6-83F7-61ED15F61DDB}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q3" dataDxfId="40"/>
-    <tableColumn id="18" xr3:uid="{56F2625D-2CEE-478E-A8DE-42A7191C3835}" name="Year of Delivery-LAS - Q3" dataDxfId="39"/>
-    <tableColumn id="19" xr3:uid="{EF0F614F-5FED-4639-8798-840D9677B8DA}" name="SOURCE-LAS (CO,RO, SDO) - Q3" dataDxfId="38"/>
-    <tableColumn id="20" xr3:uid="{FD91DDEE-DBA8-4E2C-94B2-23AE9F73CC4A}" name="GAP - LAS - Q3" dataDxfId="37">
+    <tableColumn id="17" xr3:uid="{48667A1F-77B1-47A6-83F7-61ED15F61DDB}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q3" dataDxfId="43"/>
+    <tableColumn id="18" xr3:uid="{56F2625D-2CEE-478E-A8DE-42A7191C3835}" name="Year of Delivery-LAS - Q3" dataDxfId="42"/>
+    <tableColumn id="19" xr3:uid="{EF0F614F-5FED-4639-8798-840D9677B8DA}" name="SOURCE-LAS (CO,RO, SDO) - Q3" dataDxfId="41"/>
+    <tableColumn id="20" xr3:uid="{FD91DDEE-DBA8-4E2C-94B2-23AE9F73CC4A}" name="GAP - LAS - Q3" dataDxfId="40">
       <calculatedColumnFormula>IF((P3-Q3)&lt;0,0,(P3-Q3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{DB598C6C-E489-4B0F-9BC6-B0981F7D2582}" name="SURPLUS - LAS - Q3" dataDxfId="36">
+    <tableColumn id="21" xr3:uid="{DB598C6C-E489-4B0F-9BC6-B0981F7D2582}" name="SURPLUS - LAS - Q3" dataDxfId="39">
       <calculatedColumnFormula>IF((Q3-P3)&lt;0,0,(Q3-P3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{8CD6906A-7980-46E8-80B2-8563AEBC71F7}" name="Quantity based on Target LAS - Q4" dataDxfId="35">
+    <tableColumn id="22" xr3:uid="{8CD6906A-7980-46E8-80B2-8563AEBC71F7}" name="Quantity based on Target LAS - Q4" dataDxfId="38">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{6287B1E4-D2AD-47C7-BD86-3391F339B1E3}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS)- Q4" dataDxfId="34"/>
-    <tableColumn id="24" xr3:uid="{205BCDBA-0424-492C-B4EF-841B8A3A1521}" name="Year of Delivery - LAS - Q4" dataDxfId="33"/>
-    <tableColumn id="25" xr3:uid="{8226E35B-1F3B-4D2A-815B-9D4C0A24EE7E}" name="SOURCE - LAS (CO,RO, SDO) - Q4" dataDxfId="32"/>
-    <tableColumn id="26" xr3:uid="{5B37A4B7-CD16-4D9A-8A47-D9EA73F613BC}" name="GAP - LAS - Q4" dataDxfId="31">
+    <tableColumn id="23" xr3:uid="{6287B1E4-D2AD-47C7-BD86-3391F339B1E3}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS)- Q4" dataDxfId="37"/>
+    <tableColumn id="24" xr3:uid="{205BCDBA-0424-492C-B4EF-841B8A3A1521}" name="Year of Delivery - LAS - Q4" dataDxfId="36"/>
+    <tableColumn id="25" xr3:uid="{8226E35B-1F3B-4D2A-815B-9D4C0A24EE7E}" name="SOURCE - LAS (CO,RO, SDO) - Q4" dataDxfId="35"/>
+    <tableColumn id="26" xr3:uid="{5B37A4B7-CD16-4D9A-8A47-D9EA73F613BC}" name="GAP - LAS - Q4" dataDxfId="34">
       <calculatedColumnFormula>IF((V3-W3)&lt;0,0,(V3-W3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{38E9C5F3-3FF5-4B13-A9DA-0081A90F35C5}" name="SURPLUS - LAS - Q4" dataDxfId="30">
+    <tableColumn id="27" xr3:uid="{38E9C5F3-3FF5-4B13-A9DA-0081A90F35C5}" name="SURPLUS - LAS - Q4" dataDxfId="33">
       <calculatedColumnFormula>IF((W3-V3)&lt;0,0,(W3-V3))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3092,7 +3098,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
   <autoFilter ref="A2:AA140" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
@@ -3465,17 +3471,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H98"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.0859375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="5" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1015625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" customWidth="1"/>
     <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
+    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -3501,7 +3507,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="42.75" customHeight="1">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3511,19 +3517,25 @@
       <c r="C2" s="1">
         <v>26</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="5"/>
+      <c r="D2" s="1">
+        <v>33</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G2" s="3">
         <f>IF((C2-D2)&lt;0,0,C2-D2)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H2" s="4">
         <f>IF((D2-C2)&lt;0,0,D2-C2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="29.25" customHeight="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3533,19 +3545,25 @@
       <c r="C3" s="1">
         <v>26</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="5"/>
+      <c r="D3" s="1">
+        <v>33</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G3" s="3">
         <f>IF((C3-D3)&lt;0,0,C3-D3)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H3" s="4">
         <f>IF((D3-C3)&lt;0,0,D3-C3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="21" customHeight="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3555,19 +3573,25 @@
       <c r="C4" s="1">
         <v>26</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="5"/>
+      <c r="D4" s="1">
+        <v>33</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G4" s="3">
         <f>IF((C4-D4)&lt;0,0,C4-D4)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H4" s="4">
         <f>IF((D4-C4)&lt;0,0,D4-C4)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="25.5" customHeight="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3577,19 +3601,25 @@
       <c r="C5" s="1">
         <v>26</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="5"/>
+      <c r="D5" s="1">
+        <v>33</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G5" s="3">
         <f t="shared" ref="G5:G6" si="0">IF((C5-D5)&lt;0,0,C5-D5)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" ref="H5:H6" si="1">IF((D5-C5)&lt;0,0,D5-C5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="19.5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3611,12 +3641,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="39.75" customHeight="1">
+    <row r="8" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -3638,7 +3668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" customHeight="1">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -3660,7 +3690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" customHeight="1">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3682,7 +3712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1">
+    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3692,19 +3722,25 @@
       <c r="C11" s="1">
         <v>18</v>
       </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+      <c r="D11" s="1">
+        <v>38</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="19.5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3726,12 +3762,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="49.5" customHeight="1">
+    <row r="14" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -3753,7 +3789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29.25" customHeight="1">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -3775,7 +3811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" customHeight="1">
+    <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>3</v>
       </c>
@@ -3797,7 +3833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" customHeight="1">
+    <row r="17" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>3</v>
       </c>
@@ -3819,7 +3855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" customHeight="1">
+    <row r="18" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>3</v>
       </c>
@@ -3841,7 +3877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.5">
+    <row r="19" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3863,7 +3899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3873,7 +3909,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" customHeight="1">
+    <row r="21" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>4</v>
       </c>
@@ -3895,7 +3931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="24" customHeight="1">
+    <row r="22" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -3905,19 +3941,25 @@
       <c r="C22" s="1">
         <v>14</v>
       </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="5"/>
+      <c r="D22" s="1">
+        <v>40</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="19.5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -3927,19 +3969,25 @@
       <c r="C23" s="1">
         <v>14</v>
       </c>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="5"/>
+      <c r="D23" s="1">
+        <v>40</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="27" customHeight="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>4</v>
       </c>
@@ -3949,19 +3997,25 @@
       <c r="C24" s="1">
         <v>14</v>
       </c>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="5"/>
+      <c r="D24" s="1">
+        <v>40</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="33.75" customHeight="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -3971,19 +4025,25 @@
       <c r="C25" s="1">
         <v>14</v>
       </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="5"/>
+      <c r="D25" s="1">
+        <v>40</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="33.75" customHeight="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>4</v>
       </c>
@@ -3993,19 +4053,25 @@
       <c r="C26" s="1">
         <v>14</v>
       </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="5"/>
+      <c r="D26" s="1">
+        <v>40</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H26" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="33.75" customHeight="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -4015,19 +4081,25 @@
       <c r="C27" s="1">
         <v>14</v>
       </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="5"/>
+      <c r="D27" s="1">
+        <v>40</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H27" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="27.75" customHeight="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>4</v>
       </c>
@@ -4049,7 +4121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" customHeight="1">
+    <row r="29" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -4059,19 +4131,25 @@
       <c r="C29" s="1">
         <v>14</v>
       </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="D29" s="1">
+        <v>40</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="27.75" customHeight="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -4081,7 +4159,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>5</v>
       </c>
@@ -4091,19 +4169,25 @@
       <c r="C31" s="1">
         <v>13</v>
       </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="5"/>
+      <c r="D31" s="1">
+        <v>35</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>5</v>
       </c>
@@ -4125,7 +4209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.75" customHeight="1">
+    <row r="33" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>5</v>
       </c>
@@ -4147,7 +4231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="27.75" customHeight="1">
+    <row r="34" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>5</v>
       </c>
@@ -4169,7 +4253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="39" customHeight="1">
+    <row r="35" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -4179,19 +4263,25 @@
       <c r="C35" s="1">
         <v>13</v>
       </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="5"/>
+      <c r="D35" s="1">
+        <v>35</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="27.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -4201,19 +4291,25 @@
       <c r="C36" s="1">
         <v>13</v>
       </c>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
+      <c r="D36" s="1">
+        <v>35</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="27.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>5</v>
       </c>
@@ -4223,19 +4319,25 @@
       <c r="C37" s="1">
         <v>13</v>
       </c>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="5"/>
+      <c r="D37" s="1">
+        <v>35</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="27.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>5</v>
       </c>
@@ -4245,19 +4347,25 @@
       <c r="C38" s="1">
         <v>13</v>
       </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="D38" s="1">
+        <v>35</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="27.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>5</v>
       </c>
@@ -4279,7 +4387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="27.75" customHeight="1">
+    <row r="40" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -4289,7 +4397,7 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="27.75" customHeight="1">
+    <row r="41" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>6</v>
       </c>
@@ -4311,7 +4419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="27.75" customHeight="1">
+    <row r="42" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>6</v>
       </c>
@@ -4333,7 +4441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.75" customHeight="1">
+    <row r="43" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>6</v>
       </c>
@@ -4355,7 +4463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27.75" customHeight="1">
+    <row r="44" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>6</v>
       </c>
@@ -4377,7 +4485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="36.75" customHeight="1">
+    <row r="45" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>6</v>
       </c>
@@ -4399,7 +4507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27.75" customHeight="1">
+    <row r="46" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>6</v>
       </c>
@@ -4421,7 +4529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="27.75" customHeight="1">
+    <row r="47" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>6</v>
       </c>
@@ -4443,7 +4551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.75" customHeight="1">
+    <row r="48" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>6</v>
       </c>
@@ -4465,7 +4573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" customHeight="1">
+    <row r="49" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>6</v>
       </c>
@@ -4487,7 +4595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" customHeight="1">
+    <row r="50" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
@@ -4497,7 +4605,7 @@
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" ht="27.75" customHeight="1">
+    <row r="51" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
         <v>7</v>
       </c>
@@ -4517,7 +4625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="27.75" customHeight="1">
+    <row r="52" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>7</v>
       </c>
@@ -4537,7 +4645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="27.75" customHeight="1">
+    <row r="53" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>7</v>
       </c>
@@ -4557,7 +4665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="27.75" customHeight="1">
+    <row r="54" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>7</v>
       </c>
@@ -4577,7 +4685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="39" customHeight="1">
+    <row r="55" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10">
         <v>7</v>
       </c>
@@ -4597,7 +4705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="27.75" customHeight="1">
+    <row r="56" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
         <v>7</v>
       </c>
@@ -4617,7 +4725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="27.75" customHeight="1">
+    <row r="57" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10">
         <v>7</v>
       </c>
@@ -4637,7 +4745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="27.75" customHeight="1">
+    <row r="58" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10">
         <v>7</v>
       </c>
@@ -4657,7 +4765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="27.75" customHeight="1">
+    <row r="59" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="10">
         <v>7</v>
       </c>
@@ -4677,7 +4785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="27.75" customHeight="1">
+    <row r="60" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -4687,7 +4795,7 @@
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" ht="27.75" customHeight="1">
+    <row r="61" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="10">
         <v>8</v>
       </c>
@@ -4707,7 +4815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="27.75" customHeight="1">
+    <row r="62" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="10">
         <v>8</v>
       </c>
@@ -4727,7 +4835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="27.75" customHeight="1">
+    <row r="63" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>8</v>
       </c>
@@ -4747,7 +4855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="27.75" customHeight="1">
+    <row r="64" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>8</v>
       </c>
@@ -4767,7 +4875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="27.75" customHeight="1">
+    <row r="65" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>8</v>
       </c>
@@ -4787,7 +4895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="27.75" customHeight="1">
+    <row r="66" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>8</v>
       </c>
@@ -4807,7 +4915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="27.75" customHeight="1">
+    <row r="67" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>8</v>
       </c>
@@ -4827,7 +4935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="27.75" customHeight="1">
+    <row r="68" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>8</v>
       </c>
@@ -4847,7 +4955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="27.75" customHeight="1">
+    <row r="69" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>8</v>
       </c>
@@ -4867,7 +4975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="27.75" customHeight="1">
+    <row r="70" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
@@ -4877,7 +4985,7 @@
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" ht="27.75" customHeight="1">
+    <row r="71" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>9</v>
       </c>
@@ -4897,7 +5005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="27.75" customHeight="1">
+    <row r="72" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>9</v>
       </c>
@@ -4917,7 +5025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="27.75" customHeight="1">
+    <row r="73" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>9</v>
       </c>
@@ -4937,7 +5045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="27.75" customHeight="1">
+    <row r="74" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>9</v>
       </c>
@@ -4957,7 +5065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="27.75" customHeight="1">
+    <row r="75" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>9</v>
       </c>
@@ -4977,7 +5085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="27.75" customHeight="1">
+    <row r="76" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>9</v>
       </c>
@@ -4997,7 +5105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="27.75" customHeight="1">
+    <row r="77" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>9</v>
       </c>
@@ -5017,7 +5125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="27.75" customHeight="1">
+    <row r="78" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>9</v>
       </c>
@@ -5037,7 +5145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="27.75" customHeight="1">
+    <row r="79" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>9</v>
       </c>
@@ -5057,7 +5165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="27.75" customHeight="1">
+    <row r="80" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="7"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -5067,7 +5175,7 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" ht="27.75" customHeight="1">
+    <row r="81" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>10</v>
       </c>
@@ -5087,7 +5195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="27.75" customHeight="1">
+    <row r="82" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>10</v>
       </c>
@@ -5107,7 +5215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="27.75" customHeight="1">
+    <row r="83" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>10</v>
       </c>
@@ -5127,7 +5235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="27.75" customHeight="1">
+    <row r="84" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>10</v>
       </c>
@@ -5147,7 +5255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="27.75" customHeight="1">
+    <row r="85" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>10</v>
       </c>
@@ -5167,7 +5275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="27.75" customHeight="1">
+    <row r="86" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>10</v>
       </c>
@@ -5187,7 +5295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="27.75" customHeight="1">
+    <row r="87" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>10</v>
       </c>
@@ -5207,7 +5315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="27.75" customHeight="1">
+    <row r="88" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>10</v>
       </c>
@@ -5227,7 +5335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="27.75" customHeight="1">
+    <row r="89" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>10</v>
       </c>
@@ -5247,7 +5355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="27.75" customHeight="1">
+    <row r="90" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
@@ -5257,7 +5365,7 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" ht="39.75" customHeight="1">
+    <row r="91" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>23</v>
       </c>
@@ -5277,7 +5385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="27.75" customHeight="1">
+    <row r="92" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>23</v>
       </c>
@@ -5297,7 +5405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="27.75" customHeight="1">
+    <row r="93" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>23</v>
       </c>
@@ -5317,7 +5425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="27.75" customHeight="1">
+    <row r="94" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>23</v>
       </c>
@@ -5337,7 +5445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="40.5" customHeight="1">
+    <row r="95" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>23</v>
       </c>
@@ -5357,7 +5465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="38.25" customHeight="1">
+    <row r="96" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>23</v>
       </c>
@@ -5377,7 +5485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="27.75" customHeight="1">
+    <row r="97" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>23</v>
       </c>
@@ -5397,7 +5505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="47.25" customHeight="1">
+    <row r="98" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>23</v>
       </c>
@@ -5427,7 +5535,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F91:F98 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F31:F39" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6" xr:uid="{5F3020B7-3D63-48D9-AF46-F057226AB351}">
@@ -5444,35 +5552,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
   <dimension ref="A1:AA127"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="35.5703125" customWidth="1"/>
-    <col min="12" max="12" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.5703125" customWidth="1"/>
-    <col min="14" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="33.42578125" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="26.09765625" customWidth="1"/>
+    <col min="5" max="5" width="23.13671875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5625" customWidth="1"/>
+    <col min="8" max="9" width="20.84765625" customWidth="1"/>
+    <col min="10" max="10" width="13.71875" customWidth="1"/>
+    <col min="11" max="11" width="35.51171875" customWidth="1"/>
+    <col min="12" max="12" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.609375" customWidth="1"/>
+    <col min="14" max="15" width="20.84765625" customWidth="1"/>
+    <col min="16" max="16" width="21.5234375" customWidth="1"/>
+    <col min="17" max="17" width="33.359375" customWidth="1"/>
+    <col min="18" max="18" width="25.828125" customWidth="1"/>
+    <col min="19" max="19" width="32.8203125" customWidth="1"/>
+    <col min="20" max="21" width="20.84765625" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="23" max="23" width="25.01953125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="20.84765625" customWidth="1"/>
+    <col min="26" max="26" width="14.796875" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="42" t="s">
         <v>32</v>
       </c>
@@ -5506,7 +5614,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -5589,7 +5697,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="30.6" customHeight="1">
+    <row r="3" spans="1:27" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>60</v>
       </c>
@@ -5658,7 +5766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -5670,7 +5778,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="38.25">
+    <row r="5" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5741,7 +5849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.5">
+    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5812,7 +5920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.5">
+    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5883,7 +5991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.5">
+    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -5954,7 +6062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.5">
+    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6025,7 +6133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.5">
+    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6096,7 +6204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.5">
+    <row r="11" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6167,7 +6275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.5">
+    <row r="12" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6238,7 +6346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6251,7 +6359,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="38.25">
+    <row r="14" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6322,7 +6430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.5">
+    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6393,7 +6501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.5">
+    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6464,7 +6572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.5">
+    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6535,7 +6643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.5">
+    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6606,7 +6714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.5">
+    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6677,7 +6785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.5">
+    <row r="20" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6748,7 +6856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.5">
+    <row r="21" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6819,7 +6927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6833,7 +6941,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="38.25">
+    <row r="23" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6904,7 +7012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.5">
+    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -6975,7 +7083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.5">
+    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7046,7 +7154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.5">
+    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7117,7 +7225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.5">
+    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7188,7 +7296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.5">
+    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7259,7 +7367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.5">
+    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7330,7 +7438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.5">
+    <row r="30" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7401,7 +7509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.5">
+    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7472,7 +7580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7486,7 +7594,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.5">
+    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7557,7 +7665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.5">
+    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7628,7 +7736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.5">
+    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7699,7 +7807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.5">
+    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7770,7 +7878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="38.25">
+    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7841,7 +7949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.5">
+    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7912,7 +8020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.5">
+    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -7983,7 +8091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.5">
+    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8054,7 +8162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.5">
+    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8125,7 +8233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8139,7 +8247,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.5">
+    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8210,7 +8318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.5">
+    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8281,7 +8389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.5">
+    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8352,7 +8460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.5">
+    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8423,7 +8531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="38.25">
+    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8494,7 +8602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.5">
+    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8565,7 +8673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.5">
+    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8636,7 +8744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.5">
+    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8707,7 +8815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.5">
+    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8778,7 +8886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8792,7 +8900,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.5">
+    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -8863,7 +8971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.5">
+    <row r="54" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8934,7 +9042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.5">
+    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -9005,7 +9113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.5">
+    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9076,7 +9184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="38.25">
+    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9147,7 +9255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.5">
+    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9218,7 +9326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.5">
+    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9289,7 +9397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.5">
+    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9360,7 +9468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.5">
+    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9431,7 +9539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9445,7 +9553,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9514,7 +9622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9583,7 +9691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9652,7 +9760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9721,7 +9829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9790,7 +9898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9859,7 +9967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9928,7 +10036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -9997,7 +10105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -10066,7 +10174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -10080,7 +10188,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10149,7 +10257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10218,7 +10326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10287,7 +10395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10356,7 +10464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10425,7 +10533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10494,7 +10602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10563,7 +10671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10632,7 +10740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10701,7 +10809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10715,7 +10823,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10784,7 +10892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10853,7 +10961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10922,7 +11030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -10991,7 +11099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -11060,7 +11168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11129,7 +11237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11198,7 +11306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11267,7 +11375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11336,7 +11444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11350,7 +11458,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11419,7 +11527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11488,7 +11596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11557,7 +11665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11626,7 +11734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11695,7 +11803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11764,7 +11872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11833,7 +11941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11902,7 +12010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -11971,7 +12079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -11985,7 +12093,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>23</v>
       </c>
@@ -12054,7 +12162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>23</v>
       </c>
@@ -12123,7 +12231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>23</v>
       </c>
@@ -12192,7 +12300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>23</v>
       </c>
@@ -12261,7 +12369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>23</v>
       </c>
@@ -12330,7 +12438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>23</v>
       </c>
@@ -12399,7 +12507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>23</v>
       </c>
@@ -12468,7 +12576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>23</v>
       </c>
@@ -12537,7 +12645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12548,7 +12656,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12610,7 +12718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12672,7 +12780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12734,7 +12842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12796,7 +12904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12858,7 +12966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12920,7 +13028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -12982,7 +13090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -13044,7 +13152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13106,7 +13214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13168,7 +13276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13230,7 +13338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13292,7 +13400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13354,7 +13462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13416,7 +13524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13478,7 +13586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13574,34 +13682,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
   <dimension ref="A1:AB140"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="24.42578125" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" customWidth="1"/>
-    <col min="13" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="29.140625" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="16.41015625" customWidth="1"/>
+    <col min="5" max="5" width="23.13671875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5625" customWidth="1"/>
+    <col min="8" max="9" width="20.84765625" customWidth="1"/>
+    <col min="10" max="10" width="13.71875" customWidth="1"/>
+    <col min="11" max="11" width="24.48046875" customWidth="1"/>
+    <col min="12" max="12" width="18.16015625" customWidth="1"/>
+    <col min="13" max="15" width="20.84765625" customWidth="1"/>
+    <col min="16" max="16" width="21.5234375" customWidth="1"/>
+    <col min="17" max="17" width="29.19140625" customWidth="1"/>
+    <col min="18" max="18" width="25.828125" customWidth="1"/>
+    <col min="19" max="19" width="32.8203125" customWidth="1"/>
+    <col min="20" max="21" width="20.84765625" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="23" max="23" width="25.01953125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="20.84765625" customWidth="1"/>
+    <col min="26" max="26" width="14.796875" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="35"/>
       <c r="D1" s="42" t="s">
         <v>32</v>
@@ -13636,7 +13744,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -13719,7 +13827,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="38.25">
+    <row r="3" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -13790,7 +13898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.5">
+    <row r="4" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -13861,7 +13969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.5">
+    <row r="5" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -13932,7 +14040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.5">
+    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14003,7 +14111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.5">
+    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14074,7 +14182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.5">
+    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14145,7 +14253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.5">
+    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14216,7 +14324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.5">
+    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14287,8 +14395,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="38.25">
+    <row r="11" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14359,7 +14467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.5">
+    <row r="13" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14430,7 +14538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.5">
+    <row r="14" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14501,7 +14609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.5">
+    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14572,7 +14680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.5">
+    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14643,7 +14751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.5">
+    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14714,7 +14822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.5">
+    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -14785,7 +14893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.5">
+    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -14856,8 +14964,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="38.25">
+    <row r="20" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -14928,7 +15036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.5">
+    <row r="22" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -14999,7 +15107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.5">
+    <row r="23" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15070,7 +15178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.5">
+    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15141,7 +15249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.5">
+    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15212,7 +15320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.5">
+    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15283,7 +15391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.5">
+    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15354,7 +15462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.5">
+    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15425,7 +15533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.5">
+    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15496,8 +15604,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.5">
+    <row r="30" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15568,7 +15676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.5">
+    <row r="32" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15639,7 +15747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.5">
+    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15710,7 +15818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.5">
+    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15781,7 +15889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="38.25">
+    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -15852,7 +15960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.5">
+    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -15923,7 +16031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.5">
+    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -15994,7 +16102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.5">
+    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16065,7 +16173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.5">
+    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16136,7 +16244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.5">
+    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16207,7 +16315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.5">
+    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16278,8 +16386,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.5">
+    <row r="42" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16350,7 +16458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.5">
+    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16421,7 +16529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.5">
+    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16492,7 +16600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.5">
+    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16563,7 +16671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="38.25">
+    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16634,7 +16742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.5">
+    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16705,7 +16813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.5">
+    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -16776,7 +16884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.5">
+    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -16847,7 +16955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.5">
+    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -16918,7 +17026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.5">
+    <row r="52" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -16989,7 +17097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.5">
+    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -17060,8 +17168,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.5">
+    <row r="54" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17132,7 +17240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.5">
+    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17203,7 +17311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.5">
+    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17274,7 +17382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.5">
+    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17345,7 +17453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="38.25">
+    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17416,7 +17524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.5">
+    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17487,7 +17595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.5">
+    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17558,7 +17666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.5">
+    <row r="62" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17629,7 +17737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.5">
+    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17700,7 +17808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.5">
+    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -17771,7 +17879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.5">
+    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -17842,8 +17950,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -17912,7 +18020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -17981,7 +18089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -18050,7 +18158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18119,7 +18227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18188,7 +18296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18257,7 +18365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18326,7 +18434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18395,7 +18503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18464,7 +18572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18533,7 +18641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18602,8 +18710,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18672,7 +18780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18741,7 +18849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -18810,7 +18918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18879,7 +18987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -18948,7 +19056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -19017,7 +19125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -19086,7 +19194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19155,7 +19263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19224,7 +19332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19293,7 +19401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19362,8 +19470,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19432,7 +19540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19501,7 +19609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19570,7 +19678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19639,7 +19747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19708,7 +19816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -19777,7 +19885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -19846,7 +19954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -19915,7 +20023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -19984,7 +20092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -20053,7 +20161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20122,8 +20230,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="103" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20192,7 +20300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20261,7 +20369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20330,7 +20438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20399,7 +20507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20468,7 +20576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20537,7 +20645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
+    <row r="109" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20606,7 +20714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -20675,7 +20783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20744,7 +20852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -20813,7 +20921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -20882,8 +20990,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
+    <row r="114" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="115" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>23</v>
       </c>
@@ -20952,7 +21060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>23</v>
       </c>
@@ -21021,7 +21129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>23</v>
       </c>
@@ -21090,7 +21198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>23</v>
       </c>
@@ -21159,7 +21267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>23</v>
       </c>
@@ -21228,7 +21336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>23</v>
       </c>
@@ -21297,7 +21405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>23</v>
       </c>
@@ -21366,7 +21474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>23</v>
       </c>
@@ -21435,8 +21543,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" s="7" customFormat="1"/>
-    <row r="124" spans="1:28">
+    <row r="123" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -21466,7 +21574,7 @@
       <c r="AA124" s="7"/>
       <c r="AB124" s="7"/>
     </row>
-    <row r="125" spans="1:28">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -21496,7 +21604,7 @@
       <c r="AA125" s="7"/>
       <c r="AB125" s="7"/>
     </row>
-    <row r="126" spans="1:28">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -21526,7 +21634,7 @@
       <c r="AA126" s="7"/>
       <c r="AB126" s="7"/>
     </row>
-    <row r="127" spans="1:28">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -21556,7 +21664,7 @@
       <c r="AA127" s="7"/>
       <c r="AB127" s="7"/>
     </row>
-    <row r="128" spans="1:28">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -21586,7 +21694,7 @@
       <c r="AA128" s="7"/>
       <c r="AB128" s="7"/>
     </row>
-    <row r="129" spans="1:28">
+    <row r="129" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -21616,7 +21724,7 @@
       <c r="AA129" s="7"/>
       <c r="AB129" s="7"/>
     </row>
-    <row r="130" spans="1:28">
+    <row r="130" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -21646,7 +21754,7 @@
       <c r="AA130" s="7"/>
       <c r="AB130" s="7"/>
     </row>
-    <row r="131" spans="1:28">
+    <row r="131" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -21676,7 +21784,7 @@
       <c r="AA131" s="7"/>
       <c r="AB131" s="7"/>
     </row>
-    <row r="132" spans="1:28">
+    <row r="132" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -21706,7 +21814,7 @@
       <c r="AA132" s="7"/>
       <c r="AB132" s="7"/>
     </row>
-    <row r="133" spans="1:28">
+    <row r="133" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -21736,7 +21844,7 @@
       <c r="AA133" s="7"/>
       <c r="AB133" s="7"/>
     </row>
-    <row r="134" spans="1:28">
+    <row r="134" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -21766,7 +21874,7 @@
       <c r="AA134" s="7"/>
       <c r="AB134" s="7"/>
     </row>
-    <row r="135" spans="1:28">
+    <row r="135" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -21796,7 +21904,7 @@
       <c r="AA135" s="7"/>
       <c r="AB135" s="7"/>
     </row>
-    <row r="136" spans="1:28">
+    <row r="136" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -21826,7 +21934,7 @@
       <c r="AA136" s="7"/>
       <c r="AB136" s="7"/>
     </row>
-    <row r="137" spans="1:28">
+    <row r="137" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -21856,7 +21964,7 @@
       <c r="AA137" s="7"/>
       <c r="AB137" s="7"/>
     </row>
-    <row r="138" spans="1:28">
+    <row r="138" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -21886,7 +21994,7 @@
       <c r="AA138" s="7"/>
       <c r="AB138" s="7"/>
     </row>
-    <row r="139" spans="1:28">
+    <row r="139" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -21916,7 +22024,7 @@
       <c r="AA139" s="7"/>
       <c r="AB139" s="7"/>
     </row>
-    <row r="140" spans="1:28">
+    <row r="140" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
